--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -308,7 +308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -381,6 +381,16 @@
           <t>player12</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>player13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -428,6 +438,16 @@
           <t>zuw</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>drk</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Borrachinha</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -766,6 +786,16 @@
           <t>nw</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>cailloou</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zeph</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -808,6 +838,11 @@
           <t>Kaos</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SuperPedrin</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -877,6 +912,11 @@
           <t>seki</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jotave</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -914,6 +954,11 @@
           <t>noway</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Leywin</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1000,6 +1045,11 @@
           <t>neguzera69</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>mindos</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1069,6 +1119,16 @@
           <t>Japa</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>huzuni</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Kmkz</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1148,6 +1208,11 @@
           <t>Thorfinn</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Kebi Láo</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1239,11 +1304,6 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yasuzinn</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
           <t>nx4pp</t>
         </is>
       </c>
@@ -1452,6 +1512,16 @@
           <t>Chocolate</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hirama</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>kim</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1481,22 +1551,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hirama</t>
+          <t>leanza</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>leanza</t>
+          <t>Piui</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Piui</t>
+          <t>Gabs</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Gabs</t>
+          <t>jungkook67</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Foca Não</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>EldenRot</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>zezinhoDasPARTY</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Rocha1706</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>luli</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2507,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gsN</t>
+          <t>Fillip1n</t>
         </is>
       </c>
     </row>
@@ -2479,6 +2574,16 @@
           <t>Makola</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Driblas</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Drs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2488,16 +2593,6 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Drs</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Driblas</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
           <t>Goavy</t>
         </is>
       </c>
@@ -2649,6 +2744,11 @@
           <t>vvv</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2849,6 +2949,21 @@
           <t>akashi</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>must</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>snwssj</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Blonded</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2886,6 +3001,11 @@
           <t>Rype</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>xrz</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3316,6 +3436,21 @@
           <t>Artzz</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>katori</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>bushikage</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>paivaz01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3395,6 +3530,16 @@
           <t>kyriafn</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>catdrug</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EllenDoKrav</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3407,11 +3552,6 @@
           <t>Klouzz</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>SuperPedrin</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3508,6 +3648,11 @@
           <t>Rudini</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Daybreak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3604,6 +3749,11 @@
           <t>Veloso</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>asca</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3636,6 +3786,11 @@
           <t>Jfalls</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>reyzeratr</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3668,6 +3823,11 @@
           <t>jgrb</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>yutaz</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3710,6 +3870,11 @@
           <t>Prime</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>SNZ</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3932,6 +4097,11 @@
           <t>Schroud</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Kaname</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4169,6 +4339,159 @@
       <c r="G101" t="inlineStr">
         <is>
           <t>lucKZin</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>kbcdin</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ufu_saints_trigons</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>speedzillaa</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Athos778</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ppeuz</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>trash</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>gsN</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PedroLucc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>green_owls_jacurutu</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>cavaloanão</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Yasuzinn</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MistakeZ</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Lillos</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>konnZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>nox_unievangelica</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Yuuketts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Plukas</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>sonoflickzx</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Nyols</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>eddyflickzx</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Swim</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>yDavii</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sistematica_unievangelica</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>londzx</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>mattheex</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>enzokawai</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>prido1227</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>vesper</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Aika</t>
         </is>
       </c>
     </row>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4304,6 +4304,11 @@
           <t>Kafaja</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>GLEP</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -308,7 +308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -749,6 +749,16 @@
           <t>khianh</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>GrimmW</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Arkseiro</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -959,6 +969,16 @@
           <t>Leywin</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>jotave</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>pipo166</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2243,6 +2263,11 @@
           <t>Balalov3</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PedroBSilva</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2252,25 +2277,10 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BielKuma</t>
+          <t>BD1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
-        <is>
-          <t>Death Knives</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>rektzin</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>BD1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
         <is>
           <t>BrazZ</t>
         </is>
@@ -2327,6 +2337,11 @@
           <t>Madara</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>migzzz69</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2379,6 +2394,11 @@
           <t>draCo</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Kaname</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2393,30 +2413,10 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>queculpatemeu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
-        <is>
-          <t>zx6r</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>queculpatemeu</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>sinner</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Kaizin</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
         <is>
           <t>Anorak</t>
         </is>
@@ -3199,6 +3199,11 @@
           <t>Haruauau</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>manuMist</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3939,6 +3944,26 @@
           <t>honeymoon</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>gabribs</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>BlackCat</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>caiotif</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>art3mis</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4055,6 +4080,16 @@
           <t>Gabos</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DrogaeoTL</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Daske</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4365,27 +4400,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Athos778</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ppeuz</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
           <t>trash</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>gsN</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>PedroLucc4</t>
         </is>
       </c>
     </row>
@@ -4497,6 +4512,209 @@
       <c r="G105" t="inlineStr">
         <is>
           <t>Aika</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ufrn_tirana</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>sinner</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Randon</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>zx6r</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Kaizin</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ufu_saints_onyx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ppeuz</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PedroLucc4</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>gsN</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Gutoso</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Athos778</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>cesinhas</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>azure_bears_spotline</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Karbonick</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>phmvasc</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Temmonn</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Jacare</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>GregorySouza</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cantarelli</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>MIRILO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>incinera_esports</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BielKuma</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>f1lipinho</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>rektzin</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ari$e</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Death Knives</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>azure_bears_polaris</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>typeshii</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>chikao</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>giga</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Solium</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ssob</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>atletica_sustenta</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>fei_last_dance</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>macklogic_wine</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>fei_capim</t>
         </is>
       </c>
     </row>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -1804,6 +1804,11 @@
           <t>maumau</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Nacaguma</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2584,6 +2589,11 @@
           <t>Drs</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mdz</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3964,6 +3974,11 @@
           <t>art3mis</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>aimeeaimee</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4006,6 +4021,11 @@
           <t>kharuy</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NoobViciada</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4088,6 +4108,21 @@
       <c r="I93" t="inlineStr">
         <is>
           <t>Daske</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>BigaBigato</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Thigas</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>nobukuni</t>
         </is>
       </c>
     </row>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -134,9 +134,89 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Hub Uni</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player1: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player2: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player3: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player4: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player5: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player6: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player7: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player8: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player9: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player10: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player11: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player12: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player13: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <t>Função atual de player14: Titular, Reserva ou Comissão. Deixe vazio enquanto a função não estiver confirmada. Não remova o jogador para marcar como reserva.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TeamsTable" displayName="TeamsTable" ref="A1:M97" headerRowCount="1">
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TeamsTable" displayName="TeamsTable" ref="A1:AC114" headerRowCount="1">
+  <tableColumns count="29">
     <tableColumn id="1" name="team"/>
     <tableColumn id="2" name="player1"/>
     <tableColumn id="3" name="player2"/>
@@ -150,6 +230,22 @@
     <tableColumn id="11" name="player10"/>
     <tableColumn id="12" name="player11"/>
     <tableColumn id="13" name="player12"/>
+    <tableColumn id="14" name="player13"/>
+    <tableColumn id="15" name="player14"/>
+    <tableColumn id="16" name="role1"/>
+    <tableColumn id="17" name="role2"/>
+    <tableColumn id="18" name="role3"/>
+    <tableColumn id="19" name="role4"/>
+    <tableColumn id="20" name="role5"/>
+    <tableColumn id="21" name="role6"/>
+    <tableColumn id="22" name="role7"/>
+    <tableColumn id="23" name="role8"/>
+    <tableColumn id="24" name="role9"/>
+    <tableColumn id="25" name="role10"/>
+    <tableColumn id="26" name="role11"/>
+    <tableColumn id="27" name="role12"/>
+    <tableColumn id="28" name="role13"/>
+    <tableColumn id="29" name="role14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -308,11 +404,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:AC114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="13"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -391,6 +501,76 @@
           <t>player14</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>role1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>role2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>role3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>role4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>role5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>role6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>role7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>role8</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>role9</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>role10</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>role11</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>role12</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>role13</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>role14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -438,14 +618,44 @@
           <t>zuw</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>drk</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Borrachinha</t>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -546,32 +756,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>akrasia</t>
+          <t>dnk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dnk</t>
+          <t>Vladi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vladi</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Duduka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Duduka</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Luqueta</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -665,14 +900,29 @@
           <t>Stockão</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GrimmW</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Rapunzel</t>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -707,9 +957,29 @@
           <t>piM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ScherBi</t>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -741,22 +1011,52 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washin</t>
+          <t>khianh</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>khianh</t>
+          <t>GrimmW</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>GrimmW</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>Arkseiro</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -801,9 +1101,39 @@
           <t>cailloou</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>zeph</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -820,37 +1150,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lopes</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>sobrunin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>sobrunin</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Coutinho</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kaos</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
           <t>SuperPedrin</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -924,7 +1264,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jotave</t>
+          <t>JotaVe</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Reserva</t>
         </is>
       </c>
     </row>
@@ -941,42 +1311,57 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pockaus</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dante</t>
+          <t>bada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>bada</t>
+          <t>tanizaki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>tanizaki</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>noway</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Leywin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>jotave</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
           <t>pipo166</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1070,6 +1455,36 @@
           <t>mindos</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1102,6 +1517,31 @@
           <t>Puosso</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1149,6 +1589,46 @@
           <t>Kmkz</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1173,17 +1653,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>nssj</t>
+          <t>kssarato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>kssarato</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>AsianJack</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1725,42 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Thorfinn</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
           <t>Kebi Láo</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1275,9 +1805,39 @@
           <t>Piubelli</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Vitebas</t>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1406,6 +1966,31 @@
           <t>DaviPsadelo</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1524,22 +2109,52 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tapita</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Hirama</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hirama</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
           <t>kim</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Reserva</t>
         </is>
       </c>
     </row>
@@ -1551,67 +2166,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Untrusted</t>
+          <t>Lodon6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finisher</t>
+          <t>jungkook67</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rafaelvlr</t>
+          <t>Foca Não</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lodon6</t>
+          <t>EldenRot</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>leanza</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Piui</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Gabs</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>jungkook67</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Foca Não</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>EldenRot</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
           <t>zezinhoDasPARTY</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Rocha1706</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>luli</t>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1761,52 +2361,72 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hasp</t>
+          <t>htttps</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>htttps</t>
+          <t>tiezo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiezo</t>
+          <t>Apo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Apo</t>
+          <t>Nimu KM</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gugutin</t>
+          <t>Maldito</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>fr0st</t>
+          <t>maumau</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Nimu KM</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Maldito</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>maumau</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
           <t>Nacaguma</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1818,42 +2438,52 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Albernaz</t>
+          <t>demonlz</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>demonlz</t>
+          <t>Darkzin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Darkzin</t>
+          <t>Não é o Gui</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Não é o Gui</t>
+          <t>Dizin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dizin</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Verts</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
           <t>lou</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Striker</t>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -1927,17 +2557,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thz</t>
+          <t>Purikywa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purikywa</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
           <t>th ˆˆ</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2240,37 +2890,52 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1zt</t>
+          <t>fafa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fafa</t>
+          <t>Onezera</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Onezera</t>
+          <t>ddz</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ddz</t>
+          <t>Kaytoh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaytoh</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
           <t>Balalov3</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>PedroBSilva</t>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2329,22 +2994,52 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>Madara</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>mocejogafofo</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Madara</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
           <t>migzzz69</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2361,47 +3056,67 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hiujin</t>
+          <t>suzuk</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>suzuk</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>soap</t>
+          <t>Kozolove</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kozolove</t>
+          <t>loverman</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zerando</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>loverman</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>draCo</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
           <t>Kaname</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Reserva</t>
         </is>
       </c>
     </row>
@@ -2500,19 +3215,29 @@
           <t>cks</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>shanks</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyes</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Fillip1n</t>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2566,32 +3291,62 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>piva</t>
+          <t>MV</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>Makola</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Makola</t>
+          <t>Driblas</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Driblas</t>
+          <t>Drs</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Drs</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
           <t>Mdz</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2717,6 +3472,41 @@
           <t>Odysseys</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2731,32 +3521,57 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mistic</t>
+          <t>Catioro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Catioro</t>
+          <t>KRK Ego</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KRK Ego</t>
+          <t>KRK Lucky</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KRK Lucky</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>vvv</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
           <t>LTP</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2966,12 +3781,47 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>snwssj</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
           <t>Blonded</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -2993,27 +3843,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Eizo</t>
+          <t>GalloBill</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GalloBill</t>
+          <t>Pagode</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pagode</t>
+          <t>Rype</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rype</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
           <t>xrz</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3050,17 +3925,47 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dav1</t>
+          <t>wpv</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>wpv</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
           <t>salem</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3176,42 +4081,62 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>giugiujjzl</t>
+          <t>Violetx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Violetx</t>
+          <t>Hoopa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hoopa</t>
+          <t>Brusopas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brusopas</t>
+          <t>AnaGi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>yxwuki</t>
+          <t>Haruauau</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>AnaGi</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Haruauau</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
           <t>manuMist</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3466,6 +4391,46 @@
           <t>paivaz01</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3490,22 +4455,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Malagueta</t>
+          <t>InstinctSoneca</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>InstinctSoneca</t>
+          <t>yonaha</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>yonaha</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
           <t>lule</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3537,22 +4527,42 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>catdrug</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>kyriafn</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>catdrug</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
           <t>EllenDoKrav</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3732,6 +4742,31 @@
           <t>Saiindrazin</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3801,9 +4836,29 @@
           <t>Jfalls</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>reyzeratr</t>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3843,6 +4898,36 @@
           <t>yutaz</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3862,32 +4947,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Pipão</t>
+          <t>Greed</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Prime</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Greed</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Migg</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Prime</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
           <t>SNZ</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -3966,17 +5061,47 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>caiotif</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>art3mis</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
           <t>aimeeaimee</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -4008,22 +5133,42 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bielorrusia</t>
+          <t>kharuy</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sushi</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>kharuy</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
           <t>NoobViciada</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -4040,27 +5185,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ric</t>
+          <t>Duarte</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Duarte</t>
+          <t>Anzy</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anzy</t>
+          <t>anp4</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>anp4</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
           <t>Doragon</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -4082,47 +5247,82 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Guibello</t>
+          <t>gbxz</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>gbxz</t>
+          <t>Moranguinho</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Moranguinho</t>
+          <t>Gabos</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gabos</t>
+          <t>DrogaeoTL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DrogaeoTL</t>
+          <t>BigaBigato</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Daske</t>
+          <t>Thigas</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>BigaBigato</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Thigas</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
           <t>nobukuni</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Reserva</t>
         </is>
       </c>
     </row>
@@ -4172,6 +5372,46 @@
           <t>Kaname</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4341,42 +5581,72 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GalinhaMamifera</t>
+          <t>drk</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>drk</t>
+          <t>gL X</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>gL X</t>
+          <t>Hast</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hast</t>
+          <t>ferRomantica</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ferRomantica</t>
+          <t>Borrachinha</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Borrachinha</t>
+          <t>Kafaja</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kafaja</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
           <t>GLEP</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -4421,6 +5691,41 @@
           <t>kbcdin</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4438,6 +5743,16 @@
           <t>trash</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4470,6 +5785,31 @@
           <t>konnZ</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4581,6 +5921,31 @@
           <t>GBR</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4618,6 +5983,36 @@
           <t>cesinhas</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Reserva</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4692,6 +6087,31 @@
           <t>Death Knives</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4754,7 +6174,13 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="P2:AC114" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Função inválida" error="Use Titular, Reserva ou Comissão. Deixe vazio se ainda estiver investigando." promptTitle="Função no elenco" prompt="Preencha apenas após confirmar a função atual." type="list" errorStyle="stop">
+      <formula1>"Titular,Reserva,Comissão"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
